--- a/artfynd/A 62987-2023 artfynd.xlsx
+++ b/artfynd/A 62987-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62987-2023 artfynd.xlsx
+++ b/artfynd/A 62987-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75965421</v>
+        <v>75965422</v>
       </c>
       <c r="B2" t="n">
-        <v>57575</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,28 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208250</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -720,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444161.0656807845</v>
+        <v>444273</v>
       </c>
       <c r="R2" t="n">
-        <v>6220684.147629633</v>
+        <v>6220654</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -753,24 +747,14 @@
           <t>2018-05-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-05-02</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Träskliknande marker</t>
+          <t>Växer på stenblock</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,12 +785,7 @@
         <v>75965417</v>
       </c>
       <c r="B3" t="n">
-        <v>57585</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -847,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444174.1478403518</v>
+        <v>444174</v>
       </c>
       <c r="R3" t="n">
-        <v>6220745.280901726</v>
+        <v>6220745</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -880,19 +859,9 @@
           <t>2018-05-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-05-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>75965420</v>
+        <v>75965419</v>
       </c>
       <c r="B4" t="n">
-        <v>57575</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -965,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444163.9881540777</v>
+        <v>444145</v>
       </c>
       <c r="R4" t="n">
-        <v>6220694.141136526</v>
+        <v>6220674</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -998,24 +962,14 @@
           <t>2018-05-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-05-02</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äggklumpar, 20-tal</t>
+          <t>Romklump</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,15 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>75965422</v>
+        <v>75965420</v>
       </c>
       <c r="B5" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,27 +1008,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>208250</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1087,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444272.9310934737</v>
+        <v>444164</v>
       </c>
       <c r="R5" t="n">
-        <v>6220654.269922533</v>
+        <v>6220694</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1120,24 +1070,14 @@
           <t>2018-05-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-05-02</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växer på stenblock</t>
+          <t>Äggklumpar, 20-tal</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,15 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>75965418</v>
+        <v>75965421</v>
       </c>
       <c r="B6" t="n">
-        <v>55649</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,28 +1116,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208255</v>
+        <v>208250</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1214,10 +1145,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444135.8301073658</v>
+        <v>444161</v>
       </c>
       <c r="R6" t="n">
-        <v>6220719.029263741</v>
+        <v>6220684</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1247,19 +1178,14 @@
           <t>2018-05-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-05-02</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Träskliknande marker</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,15 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>75965419</v>
+        <v>75965418</v>
       </c>
       <c r="B7" t="n">
-        <v>57575</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,24 +1224,28 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208250</v>
+        <v>208255</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1332,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444144.7347584215</v>
+        <v>444136</v>
       </c>
       <c r="R7" t="n">
-        <v>6220673.771378272</v>
+        <v>6220719</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1365,24 +1290,9 @@
           <t>2018-05-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2018-05-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Romklump</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 62987-2023 artfynd.xlsx
+++ b/artfynd/A 62987-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75965422</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75965417</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75965419</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75965420</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75965421</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1317,8 +1347,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75965418</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>